--- a/Assets/07.Excel/GameData.xlsx
+++ b/Assets/07.Excel/GameData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\공부\용용죽겠지\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\My Dragon Defense\my-2D-Dragon-Defense\Assets\07.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2454E702-F050-4E1E-A918-B49FC9C6FAF1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A5CAE3-1C4A-4222-9B40-C1EF67DD3118}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" activeTab="2" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,101 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkDelay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫번째</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두번째</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>….</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1성 첫번째 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3성 첫번째 유닛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1성 첫번째 적</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -41,6 +129,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="180" formatCode="000"/>
+    <numFmt numFmtId="181" formatCode="00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -58,15 +150,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -74,13 +184,116 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -88,6 +301,75 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -404,25 +686,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09ACB276-9A8E-4EAC-977B-709B2D06B097}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="10" width="16.69921875" style="2" customWidth="1"/>
+    <col min="1" max="6" width="16.69921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="36.69921875" style="2" customWidth="1"/>
+    <col min="8" max="10" width="16.69921875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>10001001</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -454,12 +770,117 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6AABB4-23B6-45A4-B940-3702B17F6946}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="13" width="16.69921875" customWidth="1"/>
+    <col min="1" max="1" width="16.69921875" style="3" customWidth="1"/>
+    <col min="2" max="3" width="16.69921875" style="5" customWidth="1"/>
+    <col min="4" max="11" width="16.69921875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.69921875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="16.69921875" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E1" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="23"/>
+      <c r="H1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="25"/>
+      <c r="K1" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="19"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="12">
+        <v>1</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="12">
+        <v>1</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="3">
+        <v>10001001</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B3" s="8">
+        <v>20</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="14">
+        <v>2</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="14">
+        <v>2</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="3">
+        <v>10003001</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="E4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="H4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="K4" s="3">
+        <v>20001001</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="E4:F4"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Assets/07.Excel/GameData.xlsx
+++ b/Assets/07.Excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\My Dragon Defense\my-2D-Dragon-Defense\Assets\07.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A5CAE3-1C4A-4222-9B40-C1EF67DD3118}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4E05FF-A49B-4701-A077-4E652D3F3E82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" xr2:uid="{698F8AFA-8894-42B5-A618-49D138110CB8}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,6 +122,10 @@
   </si>
   <si>
     <t>1성 첫번째 적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooltime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -129,9 +133,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="180" formatCode="000"/>
-    <numFmt numFmtId="181" formatCode="00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="000"/>
+    <numFmt numFmtId="177" formatCode="00"/>
+    <numFmt numFmtId="181" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -293,7 +298,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -303,73 +308,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -691,7 +699,8 @@
   <cols>
     <col min="1" max="6" width="16.69921875" style="2" customWidth="1"/>
     <col min="7" max="7" width="36.69921875" style="2" customWidth="1"/>
-    <col min="8" max="10" width="16.69921875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.69921875" style="26" customWidth="1"/>
+    <col min="9" max="10" width="16.69921875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.4">
@@ -716,7 +725,9 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
+      <c r="H1" s="26" t="s">
+        <v>24</v>
+      </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
@@ -738,6 +749,9 @@
       </c>
       <c r="F2" s="2">
         <v>100</v>
+      </c>
+      <c r="H2" s="26">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -781,21 +795,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="23"/>
-      <c r="H1" s="24" t="s">
+      <c r="F1" s="19"/>
+      <c r="H1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="K1" s="18" t="s">
+      <c r="I1" s="21"/>
+      <c r="K1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="19"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="6">
@@ -804,7 +818,7 @@
       <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="12">
@@ -813,7 +827,7 @@
       <c r="F2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="12">
@@ -858,14 +872,14 @@
     <row r="4" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="10"/>
       <c r="C4" s="11"/>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="H4" s="16" t="s">
+      <c r="F4" s="23"/>
+      <c r="H4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="17"/>
+      <c r="I4" s="23"/>
       <c r="K4" s="3">
         <v>20001001</v>
       </c>
